--- a/ubr3enrichmentlogo/dipeptide_analysis/Dipeptide_P2P3_analysis.xlsx
+++ b/ubr3enrichmentlogo/dipeptide_analysis/Dipeptide_P2P3_analysis.xlsx
@@ -14,13 +14,15 @@
     <sheet name="TopHits_PT" sheetId="5" r:id="rId5"/>
     <sheet name="TopHits_GE" sheetId="6" r:id="rId6"/>
     <sheet name="TopHits_GD" sheetId="7" r:id="rId7"/>
+    <sheet name="TopHits_PD_PE_PT" sheetId="8" r:id="rId8"/>
+    <sheet name="TopHits_GE_GD" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="79">
   <si>
     <t>Dipeptide</t>
   </si>
@@ -62,6 +64,12 @@
   </si>
   <si>
     <t>GD</t>
+  </si>
+  <si>
+    <t>PD+PE+PT</t>
+  </si>
+  <si>
+    <t>GE+GD</t>
   </si>
   <si>
     <t>All Screen</t>
@@ -608,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -645,7 +653,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2">
         <v>23</v>
@@ -674,7 +682,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -703,7 +711,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4">
         <v>47</v>
@@ -732,7 +740,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -755,7 +763,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6">
         <v>34</v>
@@ -784,7 +792,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -813,7 +821,7 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8">
         <v>57</v>
@@ -842,7 +850,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -871,7 +879,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10">
         <v>52</v>
@@ -900,7 +908,7 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C11">
         <v>6</v>
@@ -922,6 +930,122 @@
       </c>
       <c r="I11">
         <v>3.010628135124996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <v>104</v>
+      </c>
+      <c r="D12">
+        <v>2.48996074533173</v>
+      </c>
+      <c r="E12">
+        <v>2.50840444175</v>
+      </c>
+      <c r="F12">
+        <v>0.7906867428531635</v>
+      </c>
+      <c r="G12">
+        <v>0.0775332140566808</v>
+      </c>
+      <c r="H12">
+        <v>1.719336346625</v>
+      </c>
+      <c r="I12">
+        <v>3.247920239874996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13">
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <v>1.834958760124999</v>
+      </c>
+      <c r="E13">
+        <v>1.7676675555</v>
+      </c>
+      <c r="F13">
+        <v>0.3931078288079594</v>
+      </c>
+      <c r="G13">
+        <v>0.1389846057438143</v>
+      </c>
+      <c r="H13">
+        <v>1.496252279124999</v>
+      </c>
+      <c r="I13">
+        <v>2.102938168</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14">
+        <v>109</v>
+      </c>
+      <c r="D14">
+        <v>2.836383951426605</v>
+      </c>
+      <c r="E14">
+        <v>2.915751955</v>
+      </c>
+      <c r="F14">
+        <v>0.6936923245893851</v>
+      </c>
+      <c r="G14">
+        <v>0.06644367423478759</v>
+      </c>
+      <c r="H14">
+        <v>2.3091581105</v>
+      </c>
+      <c r="I14">
+        <v>3.422174339</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15">
+        <v>12</v>
+      </c>
+      <c r="D15">
+        <v>2.561750653624999</v>
+      </c>
+      <c r="E15">
+        <v>2.520013721999997</v>
+      </c>
+      <c r="F15">
+        <v>0.3934025697999337</v>
+      </c>
+      <c r="G15">
+        <v>0.1135655397869411</v>
+      </c>
+      <c r="H15">
+        <v>2.233000924125</v>
+      </c>
+      <c r="I15">
+        <v>2.83305669175</v>
       </c>
     </row>
   </sheetData>
@@ -931,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -939,25 +1063,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -983,7 +1107,7 @@
         <v>0.3557821827745328</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1006,7 +1130,7 @@
         <v>-0.5387472030106375</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1032,7 +1156,7 @@
         <v>0.06021245311157399</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1058,7 +1182,7 @@
         <v>0.5196084316420828</v>
       </c>
       <c r="H5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1084,6 +1208,58 @@
         <v>0.03742823535430063</v>
       </c>
       <c r="H6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>104</v>
+      </c>
+      <c r="D7">
+        <v>1.834958760124999</v>
+      </c>
+      <c r="E7">
+        <v>2.48996074533173</v>
+      </c>
+      <c r="F7">
+        <v>-0.6550019852067308</v>
+      </c>
+      <c r="G7">
+        <v>0.03227813112520322</v>
+      </c>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>109</v>
+      </c>
+      <c r="D8">
+        <v>2.561750653624999</v>
+      </c>
+      <c r="E8">
+        <v>2.836383951426605</v>
+      </c>
+      <c r="F8">
+        <v>-0.2746332978016057</v>
+      </c>
+      <c r="G8">
+        <v>0.1021206731583957</v>
+      </c>
+      <c r="H8" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1099,36 +1275,36 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1139,16 +1315,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1159,16 +1335,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1189,36 +1365,36 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" t="s">
         <v>40</v>
       </c>
-      <c r="B2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" t="s">
-        <v>38</v>
-      </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -1239,36 +1415,36 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
@@ -1279,16 +1455,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -1299,16 +1475,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
@@ -1319,16 +1495,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -1349,36 +1525,36 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -1389,16 +1565,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1409,16 +1585,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
@@ -1429,16 +1605,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -1449,16 +1625,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
@@ -1469,16 +1645,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -1499,36 +1675,36 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -1539,16 +1715,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -1559,16 +1735,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
@@ -1579,16 +1755,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -1599,16 +1775,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
@@ -1619,21 +1795,481 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
       </c>
       <c r="F7">
+        <v>3.042253528499995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2">
+        <v>1.513190544</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>2.4181994905</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4">
+        <v>1.445437484499995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>1.8325557515</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>1.7027793595</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>1.407277099999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>2.0257611605</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9">
+        <v>2.3344691905</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2">
+        <v>2.578459672999995</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3">
+        <v>2.0575220875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4">
+        <v>2.0868051865</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>2.461567771</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>2.2587339895</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>2.805491604</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>2.680084658</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9">
+        <v>2.155801728</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10">
+        <v>2.4245752655</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11">
+        <v>2.915751955</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12">
+        <v>3.273960397</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13">
         <v>3.042253528499995</v>
       </c>
     </row>
